--- a/src/StaticSettingsTests/ValueRendererForSpecificType.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForSpecificType.Test.verified.xlsx
@@ -92,10 +92,10 @@
   </sheetData>
   <autoFilter ref="A1:C2"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: White-ish." sqref="B2:B2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: White-ish." prompt="Select one of: White-ish." sqref="B2:B2">
       <formula1>"White-ish"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: BUILDYOURDREAM." sqref="C2:C2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: BUILDYOURDREAM." prompt="Select one of: BUILDYOURDREAM." sqref="C2:C2">
       <formula1>"BUILDYOURDREAM"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/StaticSettingsTests/ValueRendererForSpecificType.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForSpecificType.Test.verified.xlsx
@@ -92,10 +92,10 @@
   </sheetData>
   <autoFilter ref="A1:C2"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: White-ish." prompt="Select one of: White-ish." sqref="B2:B2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: White-ish." prompt="Select one of: White-ish" sqref="B2:B2">
       <formula1>"White-ish"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: BUILDYOURDREAM." prompt="Select one of: BUILDYOURDREAM." sqref="C2:C2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: BUILDYOURDREAM." prompt="Select one of: BUILDYOURDREAM" sqref="C2:C2">
       <formula1>"BUILDYOURDREAM"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/StaticSettingsTests/ValueRendererForSpecificType.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForSpecificType.Test.verified.xlsx
@@ -92,10 +92,10 @@
   </sheetData>
   <autoFilter ref="A1:C2"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: White-ish." sqref="B2:B2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: White-ish." prompt="Select one of: White-ish" sqref="B2:B2">
       <formula1>"White-ish"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: BUILDYOURDREAM." sqref="C2:C2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: BUILDYOURDREAM." prompt="Select one of: BUILDYOURDREAM" sqref="C2:C2">
       <formula1>"BUILDYOURDREAM"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/StaticSettingsTests/ValueRendererForSpecificType.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForSpecificType.Test.verified.xlsx
@@ -103,7 +103,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
   <sheet name="Sheet1">
     <column index="1" property="Name"/>
     <column index="2" property="Color"/>
